--- a/questionnaire_templates/028_user_registration_and_timeline_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/028_user_registration_and_timeline_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>coach_comments</t>
+          <t>coach_comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Coach Comments</t>
+          <t>Coach Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>coach_comments</t>
+          <t>coach_comments_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Coach Comments</t>
+          <t>Coach Comments 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>coach_comments</t>
+          <t>coach_comments_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Coach Comments</t>
+          <t>Coach Comments 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>program_details</t>
+          <t>program_details_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Program Details</t>
+          <t>Program Details 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
